--- a/2025-26/production_value/missing_players.xlsx
+++ b/2025-26/production_value/missing_players.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A103"/>
+  <dimension ref="A1:A104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,621 +529,628 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>David Jones Garcia</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DeJon Jarreau</t>
+          <t>David Jones Garcia</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Drew Peterson</t>
+          <t>DeJon Jarreau</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Drew Peterson</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egor Demin</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Elijah Harkless</t>
+          <t>Egor Demin</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ethan Thompson</t>
+          <t>Elijah Harkless</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Isaiah Crawford</t>
+          <t>Ethan Thompson</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Isaiah Livers</t>
+          <t>Isaiah Crawford</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Isaiah Livers</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jahmir Young</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jalen Slawson</t>
+          <t>Jahmir Young</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jamal Cain</t>
+          <t>Jalen Slawson</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jamaree Bouyea</t>
+          <t>Jamal Cain</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Jamaree Bouyea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Javonte Cooke</t>
+          <t>Javon Small</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>John Poulakidas</t>
+          <t>Javonte Cooke</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Johnny Juzang</t>
+          <t>John Poulakidas</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Julian Reese</t>
+          <t>Johnny Juzang</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kennedy Chandler</t>
+          <t>Julian Reese</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kevin McCullar Jr.</t>
+          <t>Kennedy Chandler</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Kevin McCullar Jr.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lachlan Olbrich</t>
+          <t>KJ Simpson</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Leaky Black</t>
+          <t>Lachlan Olbrich</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LJ Cryer</t>
+          <t>Leaky Black</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Luke Travers</t>
+          <t>LJ Cryer</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Malevy Leons</t>
+          <t>Luke Travers</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MarJon Beauchamp</t>
+          <t>Malevy Leons</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Miles Kelly</t>
+          <t>MarJon Beauchamp</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Moussa Cisse</t>
+          <t>Miles Kelly</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nate Williams</t>
+          <t>Moussa Cisse</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Omer Yurtseven</t>
+          <t>Nate Williams</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Oscar Tshiebwe</t>
+          <t>Omer Yurtseven</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Oscar Tshiebwe</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PJ Hall</t>
+          <t>Pete Nance</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>PJ Hall</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RayJ Dennis</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ron Harper Jr.</t>
+          <t>RayJ Dennis</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ronald Holland II</t>
+          <t>Ron Harper Jr.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ryan Nembhard</t>
+          <t>Ronald Holland II</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sharife Cooper</t>
+          <t>Ryan Nembhard</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Sharife Cooper</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Taj Gibson</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tolu Smith</t>
+          <t>Taj Gibson</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Trey Jemison III</t>
+          <t>Tolu Smith</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Trey Jemison III</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tyler Burton</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tyson Etienne</t>
+          <t>Tyler Burton</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TyTy Washington Jr.</t>
+          <t>Tyson Etienne</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wendell Moore Jr.</t>
+          <t>TyTy Washington Jr.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Yuki Kawamura</t>
+          <t>Wendell Moore Jr.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>brandon clarke</t>
+          <t>Yuki Kawamura</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>charles bassey</t>
+          <t>brandon clarke</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dalano banton</t>
+          <t>charles bassey</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>damian lillard</t>
+          <t>dalano banton</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dante exum</t>
+          <t>damian lillard</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dario saric</t>
+          <t>dante exum</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dariq whitehead</t>
+          <t>dario saric</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>didi louzada</t>
+          <t>dariq whitehead</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dillon jones</t>
+          <t>didi louzada</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>egor dmin</t>
+          <t>dillon jones</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>fred vanvleet</t>
+          <t>egor dmin</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gabe mcglothan</t>
+          <t>fred vanvleet</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>georges niang</t>
+          <t>gabe mcglothan</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>grant nelson</t>
+          <t>georges niang</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>isaac jones</t>
+          <t>grant nelson</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>jaden springer</t>
+          <t>isaac jones</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>javale mcgee</t>
+          <t>jaden springer</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>john tonje</t>
+          <t>javale mcgee</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>keon johnson</t>
+          <t>john tonje</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>keshon gilbert</t>
+          <t>keon johnson</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kyrie irving</t>
+          <t>keshon gilbert</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lawson lovering</t>
+          <t>kyrie irving</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mac mcclung</t>
+          <t>lawson lovering</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mamadi diakite</t>
+          <t>mac mcclung</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mo bamba</t>
+          <t>mamadi diakite</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>n'faly dante</t>
+          <t>mo bamba</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nassir little</t>
+          <t>n'faly dante</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nikola djurisic</t>
+          <t>nassir little</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>noa essengue</t>
+          <t>nikola djurisic</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ricky rubio</t>
+          <t>noa essengue</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ron holland</t>
+          <t>ricky rubio</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>skal labissiere</t>
+          <t>ron holland</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>terry rozier</t>
+          <t>skal labissiere</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>thomas sorber</t>
+          <t>terry rozier</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tyler smith</t>
+          <t>thomas sorber</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tyrese haliburton</t>
+          <t>tyler smith</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
+        <is>
+          <t>tyrese haliburton</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>vasilije micic</t>
         </is>
